--- a/TestData/Labour.xlsx
+++ b/TestData/Labour.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10730" windowHeight="3480" firstSheet="4" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16130" windowHeight="7320" firstSheet="3" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,9 +17,10 @@
     <sheet name="Sheet8" sheetId="8" r:id="rId8"/>
     <sheet name="Sheet9" sheetId="9" r:id="rId9"/>
     <sheet name="Sheet10" sheetId="10" r:id="rId10"/>
+    <sheet name="Sheet11" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:I10"/>
+  <oleSize ref="A1:P23"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="60">
   <si>
     <t>Url</t>
   </si>
@@ -91,115 +92,124 @@
     <t>https://labour.teamleaseregtech.com</t>
   </si>
   <si>
-    <t>compliance@1234</t>
-  </si>
-  <si>
     <t>mahesh.darandale@tlregtech.in</t>
   </si>
   <si>
+    <t>reviewer.reviewer@gmail.com</t>
+  </si>
+  <si>
+    <t>admin@123</t>
+  </si>
+  <si>
+    <t>clientportal@tcg.com</t>
+  </si>
+  <si>
+    <t>AK@GN.COM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clientportal@tcg.com   </t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Maharashtra</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Satara</t>
+  </si>
+  <si>
+    <t>Branch</t>
+  </si>
+  <si>
+    <t>Emp Name</t>
+  </si>
+  <si>
+    <t>Riya</t>
+  </si>
+  <si>
+    <t>Emp Mail Id</t>
+  </si>
+  <si>
+    <t>riya@gmail.com</t>
+  </si>
+  <si>
+    <t>Emp Address</t>
+  </si>
+  <si>
+    <t>Katarj</t>
+  </si>
+  <si>
+    <t>Emp Contact</t>
+  </si>
+  <si>
+    <t>Male count</t>
+  </si>
+  <si>
+    <t>Female count</t>
+  </si>
+  <si>
+    <t>Manager Mail Id</t>
+  </si>
+  <si>
+    <t>anushree@gmail.com</t>
+  </si>
+  <si>
+    <t>Contact No</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Thane</t>
+  </si>
+  <si>
+    <t>Noitce No</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>https://labour-uat.teamleaseregtech.com/Login</t>
+  </si>
+  <si>
+    <t>swapnil.bhosle@tlregtech.in</t>
+  </si>
+  <si>
+    <t>Admin@123</t>
+  </si>
+  <si>
+    <t>KV@GN.COM</t>
+  </si>
+  <si>
+    <t>RCP@GN.COM</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> admin@123</t>
+  </si>
+  <si>
+    <t>SHRI@GN.COM</t>
+  </si>
+  <si>
+    <t>admin@1234</t>
+  </si>
+  <si>
+    <t>https://labour.teamleaseregtech.com/Login</t>
+  </si>
+  <si>
+    <t>labour URL</t>
+  </si>
+  <si>
+    <t>Perfoemer UAT</t>
+  </si>
+  <si>
     <t>teamlease@123</t>
   </si>
   <si>
-    <t>reviewer.reviewer@gmail.com</t>
-  </si>
-  <si>
-    <t>admin@123</t>
-  </si>
-  <si>
-    <t>clientportal@tcg.com</t>
-  </si>
-  <si>
-    <t>AK@GN.COM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">clientportal@tcg.com   </t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>Maharashtra</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Satara</t>
-  </si>
-  <si>
-    <t>Branch</t>
-  </si>
-  <si>
-    <t>Emp Name</t>
-  </si>
-  <si>
-    <t>Riya</t>
-  </si>
-  <si>
-    <t>Emp Mail Id</t>
-  </si>
-  <si>
-    <t>riya@gmail.com</t>
-  </si>
-  <si>
-    <t>Emp Address</t>
-  </si>
-  <si>
-    <t>Katarj</t>
-  </si>
-  <si>
-    <t>Emp Contact</t>
-  </si>
-  <si>
-    <t>Male count</t>
-  </si>
-  <si>
-    <t>Female count</t>
-  </si>
-  <si>
-    <t>Manager Mail Id</t>
-  </si>
-  <si>
-    <t>anushree@gmail.com</t>
-  </si>
-  <si>
-    <t>Contact No</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>Thane</t>
-  </si>
-  <si>
-    <t>Noitce No</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>https://labour-uat.teamleaseregtech.com/Login</t>
-  </si>
-  <si>
-    <t>swapnil.bhosle@tlregtech.in</t>
-  </si>
-  <si>
-    <t>Admin@123</t>
-  </si>
-  <si>
-    <t>KV@GN.COM</t>
-  </si>
-  <si>
-    <t>RCP@GN.COM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> admin@123</t>
-  </si>
-  <si>
-    <t>SHRI@GN.COM</t>
-  </si>
-  <si>
-    <t>admin@1234</t>
+    <t>performer@tcg.com</t>
   </si>
 </sst>
 </file>
@@ -576,7 +586,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -670,7 +680,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -678,12 +688,58 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="44.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -713,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -773,7 +829,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -781,7 +837,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -879,7 +935,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -887,7 +943,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -922,7 +978,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -930,7 +986,15 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -980,7 +1044,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -988,60 +1052,60 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B11">
         <v>3059427890</v>
@@ -1049,7 +1113,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B12">
         <v>2</v>
@@ -1057,7 +1121,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -1065,15 +1129,15 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B15">
         <v>3728476789</v>
@@ -1081,15 +1145,15 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5">
         <v>3535</v>
@@ -1100,7 +1164,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
@@ -1108,7 +1172,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
@@ -1116,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
@@ -1124,7 +1188,7 @@
         <v>1</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
@@ -1132,7 +1196,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1172,7 +1236,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1180,7 +1244,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1214,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -1222,7 +1286,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
